--- a/parser/data/xlsx/model_initialization.xlsx
+++ b/parser/data/xlsx/model_initialization.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0a05cb32-2700-44d7-b6c8-e69700564f6f</t>
+          <t>393be70b-2760-4402-b968-a900df46a52e</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c24603f2_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787_final.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/model_initialization.xlsx
+++ b/parser/data/xlsx/model_initialization.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>393be70b-2760-4402-b968-a900df46a52e</t>
+          <t>d2991275-8bd1-4891-9a74-05fac8c1f674</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_0b0ba787_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34_final.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/model_initialization.xlsx
+++ b/parser/data/xlsx/model_initialization.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>d2991275-8bd1-4891-9a74-05fac8c1f674</t>
+          <t>0cdce9cb-7efe-4ba2-b745-2071ff6b7348</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_7ee3ce34_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75_final.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/model_initialization.xlsx
+++ b/parser/data/xlsx/model_initialization.xlsx
@@ -418,7 +418,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="109" customWidth="1" min="2" max="2"/>
+    <col width="137" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0cdce9cb-7efe-4ba2-b745-2071ff6b7348</t>
+          <t>bb008549-d3df-465d-acd7-b232b9420c64</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_ca031a75_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/model_initialization.xlsx
+++ b/parser/data/xlsx/model_initialization.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bb008549-d3df-465d-acd7-b232b9420c64</t>
+          <t>3c8d9aba-e747-404c-93ba-1598590ce4e9</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\7abc486a8f2944fab510c38389cbf6f4_preprocessed_1_733e1348_final.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\5a6b5300428640cbaae38090de224504_preprocessed_1_8061a7e4_final.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/model_initialization.xlsx
+++ b/parser/data/xlsx/model_initialization.xlsx
@@ -9,6 +9,10 @@
   <sheets>
     <sheet name="record_1_metadata" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="record_1_signals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="record_2_metadata" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="record_2_signals" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="record_3_metadata" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="record_3_signals" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -614,4 +618,420 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="109" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>experiment_id</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0c3f70a1-2e88-42a5-93b3-798bdc09e68d</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dataset_path</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\data_preprocessed_1_c13340b5_final.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cols</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>is_small_data</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>is_large_data</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>is_high_dim</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>overfit_risk</t>
+        </is>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>onehot_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>freq_encoded_count</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>label_encoded_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>clustering_ready</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="137" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>experiment_id</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>c3f5ac6e-72a6-4cfb-b346-80fda5315782</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>kmeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dataset_path</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\data\42d1e5bfc1a9434c8980fd2b57f3f8d8_preprocessed_1_40ded763_final.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cols</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>is_small_data</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>is_large_data</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>is_high_dim</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>overfit_risk</t>
+        </is>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>onehot_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>freq_encoded_count</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>label_encoded_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>clustering_ready</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>